--- a/UNDP_Lebanon.xlsx
+++ b/UNDP_Lebanon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E184"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8091,6 +8091,364 @@
         </is>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Ministry of Public Works and Transport Presents Plan to Develop Public Transport in Lebanon</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/lebanon/press-releases/ministry-public-works-and-transport-presents-plan-develop-public-transport-lebanon</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>In cooperation with UNDP and under the patronage of Prime Minister Dr. Nawaf Salam
+Ministry of Public Works and Transport Presents Plan to Develop Public Transport in Lebanon
+October 26, 2026
+Beirut, 23 October 2026 – Under the patronage and in the presence of Prime Minister Dr. Nawaf Salam, the Ministry of Public Works and Transport, in cooperation with the United Nations Development Programme (UNDP), convened a high-level meeting at the Grand Serail entitled “Towards Better Public Transport in Lebanon.” The meeting presented a plan to improve public transport services, expand the network and modernise its infrastructure, and explored opportunities for the technical support, financing and investment needed for implementation, helping ease the burden of travel on citizens and support Lebanon’s economic recovery.
+The meeting brought together Minister of Public Works and Transport Fayez Rasamny; Director General of the Railway and Public Transport Authority, Eng. Ziad Shayya; and UNDP Resident Representative a.i. Thair Shraideh, alongside representatives of the Lebanese Government, public administrations and institutions, embassies and diplomatic missions, donor countries and organisations, international development partners, regional and international financial and financing institutions, and the private sector.
+The meeting comes amid challenges facing the public transport sector, particularly its limited geographical coverage, irregular services and high travel costs for citizens. Developing a more efficient, reliable and affordable transport system is a priority for easing financial pressures on households, improving access to employment, education and essential services, stimulating economic activity and strengthening connections between regions, in support of Lebanon’s recovery efforts.
+In his remarks, Prime Minister Dr. Nawaf Salam said: “Transforming public transport in Lebanon is an issue that touches the life of every citizen and lies at the heart of the economic recovery, social justice and balanced development we want for our country. The question of public transport is a question of whether employees can reach their workplaces, students their universities, and patients their hospitals. It is a question of the time we lose on the roads, the share of household income spent on travel, and the air we breathe in our cities and villages.”
+He added: “For too long, we have treated traffic congestion as inevitable and owning a private car as a natural prerequisite for working, studying and going about our lives. Yet the reality is that the absence of an alternative forces citizens to use a car or bear transport costs beyond their means. This is where our responsibility begins: to make public transport an available and reliable option that people can depend on in their daily lives.”
+He continued: “Investment in public transport is a productive investment in development and the economy, in households’ purchasing power, and in people’s health and environment. Our success will be measured by the time citizens regain from hours spent in congestion, the reduction in the costs they bear, and the greater opportunities within their reach.”
+For his part, Minister of Public Works and Transport Fayez Rasamny said: “Developing public transport in Lebanon has become an economic and social necessity and a national responsibility that cannot be postponed, amid growing pressures on living standards and rising travel costs for citizens. Our experience on the ground has demonstrated that the Lebanese people need a safe, regular and reliable alternative. The results we have achieved confirm this, as we have progressed from a standing start to carrying more than 8,000 passengers a day. Today, we are moving towards a new phase centred on developing an integrated network comprising 54 routes and around 300 buses, with a potential operating capacity of more than 60,000 passengers a day once fully implemented. Our goal is to establish a modern, sustainable and environmentally friendly transport system that connects regions to employment and service centres and provides regular, safe and accessible services for all citizens, including older persons and persons with disabilities.”
+He added: “The State is committed to assuming its responsibility in this process, recognising public transport as a public investment that serves citizens and the economy. We look forward to substantive international partnerships that support implementation, and we value our continued cooperation with UNDP and its role in supporting the Ministry’s technical work. We have made the decision and begun the work. Our responsibility now is to translate this plan into tangible results that improve the lives of the Lebanese people.”
+Director General of the Railway and Public Transport Authority, Eng. Ziad Shayya, highlighted the importance of the strategic decision taken by the Lebanese Government under Prime Minister Nawaf Salam, saying: “This decision is reflected in a clear commitment to supporting this vital sector, which cannot be considered in isolation from other sectors. It is a pillar of economic and social life and essential to society’s functioning and continuity. This underscores the importance of coordination and cooperation across all sectors, including the judiciary, security services, municipalities and the private sector, as we move towards a State whose institutions and agencies work together, forming a network of services and protection that safeguards Lebanese citizens, responds to their needs and upholds their dignity.”
+UNDP Resident Representative a.i. Thair Shraideh stressed that “investing in public transport is an investment in Lebanon’s recovery, given its role in easing the burden on households and facilitating access to employment opportunities and essential services.” He added: “Our role extends beyond supporting pilot projects to building on their results to develop scalable solutions, strengthen technical and institutional capacities, and help attract investment on a larger scale. We look forward to continuing our work with the Ministry and development partners to translate these experiences into sustainable national solutions that benefit more citizens.”
+During the meeting, Eng. Nabil Mneimne, UNDP Sustainable Transport Project Manager, delivered a technical presentation prepared by UNDP in support of the Ministry’s efforts. It outlined proposals to expand the public transport network, modernise bus fleets and infrastructure, and strengthen the sector’s institutional and operational capacities. The meeting concluded with a discussion of the technical and financing needs, as well as the partnership and investment opportunities required to advance implementation of the plan.
+The meeting forms part of the cooperation between the Ministry of Public Works and Transport and UNDP, strengthened by the signing of a memorandum of understanding in August 2026 covering technical support and capacity development in planning, implementation and sustainable infrastructure development. This cooperation also builds on practical initiatives, notably the electric bus project on the Jbeil–Beirut route, implemented with UNDP support and funding from the Global Environment Facility (GEF). The project provides practical experience that can inform the development of more sustainable transport solutions, reduce dependence on imported fuel and lessen the transport sector’s environmental impact.
+*The technical presentation is available here.</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:53:58.022272+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Germany provides €5 million to strengthen long-term stability and recovery in Lebanon</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/lebanon/press-releases/germany-provides-eur5-million-strengthen-long-term-stability-and-recovery-lebanon</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>New contribution doubles Germany’s support through UNDP programme, helping remove rubble and explosive ordnance, while sustaining the wellbeing of Lebanese Armed Forces personnel and families.
+Germany provides €5 million to strengthen long-term stability and recovery in Lebanon
+October 15, 2026
+New York, 8 October 2026 – The Government of Germany is providing an additional €5 million to the United Nations Development Programme (UNDP) to support stability and recovery in Lebanon through the country’s Lebanese Armed Forces (LAF), bringing its total contribution to the programme to €10 million. The new funding will provide equipment for rubble and explosive ordnance removal, alongside food, healthcare, education and housing support to bolster the dignity and wellbeing of LAF personnel and their families.
+The non-military assistance will continue through 2028, helping personnel meet essential needs while strengthening the LAF’s capacity to support safe access and recovery in affected communities.
+The contribution comes as the LAF faces growing responsibilities in extending State authority, in line with UN Security Council resolution 1701 (2006). These demands come amid sustained financial pressures on the institution since 2019. More than 50,000 LAF personnel and family members were displaced following the escalation of hostilities in March 2026, with returns uncertain. This comes at a time of transition in Lebanon, following the adoption of Security Council resolution 2790 (2025) to end the mandate of the United Nations Interim Force in Lebanon (UNIFIL).
+“Germany’s continued support sends a strong signal of solidarity at a decisive moment of transition for Lebanon,” said Abdallah Al Dardari, UN Assistant Secretary General and Director of UNDP’s Regional Bureau for Arab States. “Having people’s trust across Lebanon’s complex political spectrum, the Armed Forces plays a critical role in safeguarding the country’s recovery.”
+Germany has supported the programme since its launch in December 2024. Its initial €5 million contribution helped keep all 144 LAF commissaries stocked with essential food items at subsidized prices and introduced point-of-sale software across the commissary network.
+The programme provides a framework for non-military support to the LAF, supporting the wellbeing of approximately 81,500 service members and their families. It also supports the LAF’s civil-military cooperation (CIMIC) to strengthen engagement with communities and trust in State institutions.
+The programme, implemented by UNDP under a Memorandum of Understanding with Lebanon's Ministry of National Defense and the Office of the United Nations Special Coordinator for Lebanon, brings together contributions from Germany, the European Union, Spain, France, Norway, Denmark and Japan. The programme connects support for security and stability with Lebanon’s wider recovery.
+The new German contribution is provided through UNDP’s Funding Window on Governance, Peacebuilding, Crisis and Resilience. Through the same UNDP’s Funding Window, Germany has separately provided more than €6 million to the Stabilization Response Mechanism, supporting the Internal Security Forces in South Lebanon and the restoration of essential public services, including civil registry and traffic management.
+About the initiative
+The project, furthering a stronger and more focused engagement of the Lebanese Armed Forces through support to the livelihood ecosystem of its service members, runs from December 2024 to February 2028. It supports the wellbeing and food security of LAF personnel and their families, access to social services and civil-military cooperation that contributes to stabilization, recovery and renewed trust in State institutions.</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:54:07.711364+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Lebanon Launches US$20 Million Climate-Smart Matching Grants Facility to Strengthen Sustainable Agriculture</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/lebanon/press-releases/lebanon-launches-us20-million-climate-smart-matching-grants-facility-strengthen-sustainable-agriculture</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Lebanon Launches US$20 Million Climate-Smart Matching Grants Facility to Strengthen Sustainable Agriculture
+October 13, 2026
+Ministry of Agriculture, Lebanon – 13 October 2026 – The Ministry of Agriculture, the Council for Development and Reconstruction (CDR), and the United Nations Development Programme (UNDP), with funding from the World Bank, today launched the Climate-Smart Matching Grants Facility, a new initiative designed to help farmers, agricultural cooperatives and farmers’ associations invest in more productive, resilient and sustainable agriculture.
+The launch brought together H.E. Dr. Nizar Hani, Minister of Agriculture; Eng. Mohammad Ali Kabbani, President of the Council for Development and Reconstruction; Ms. Mai Ibrahim, representing the Managing Director of the World Bank Group; and Thair Shraideh, UNDP Resident Representative a.i. in Lebanon, alongside representatives of government institutions, development partners and stakeholders from Lebanon’s agricultural sector.
+Through the new facility, eligible beneficiaries can apply for climate-smart grants ranging from US$500 to US$5,000 for individual farmers and from US$10,000 to US$35,000 for agricultural cooperatives and farmers’ associations. The grants will support investments in efficient irrigation systems, renewable energy, greenhouses, agricultural machinery and equipment, storage and post-harvest facilities, processing equipment, and other climate-smart solutions and technologies. In addition to financial support, selected beneficiaries will receive training and assistance in developing business plans to help ensure the sustainability and impact of their investments.
+H.E. Dr. Nizar Hani, Minister of Agriculture, said: “We see these grants as a direct investment tool to support farmers, agricultural cooperatives and farmers’ associations, helping them reduce production costs, improve water and energy use, restore some of their damaged productive capacity, and develop more efficient and sustainable investments. Most importantly, financing will not be provided in isolation from capacity development and technical assistance. It will be complemented by training, guidance and business planning, as well as support in building sustainable links with markets and buyers. Our goal is to translate financing into better production, lower costs, higher incomes, and a stronger capacity to withstand challenges and sustain agricultural activities.”
+Eng. Mohammad Ali Kabbani, President of the Council for Development and Reconstruction, stressed: “The launch of the Climate-Smart Matching Grants Facility marks an important milestone in moving the GATE project from planning to actual implementation. We see these grants not as short-term financial assistance, but as an investment in the future of the agricultural sector and in strengthening its ability to meet emerging challenges. The success of this initiative will not be measured solely by the number of grants awarded, but by the tangible difference they make in the lives of farmers, cooperatives and agricultural associations, by ensuring transparent access to opportunities and contributing to economic recovery and sustainable development.”
+Ms. Mai Ibrahim, representing the Managing Director of the World Bank Group, highlighted the importance of the initiative, stating: “The launch of agricultural grants under the World Bank-funded GATE project marks an important step from preparation to implementation, helping support the recovery and sustainable growth of Lebanon’s agricultural sector following the significant challenges it has faced as a result of successive crises and conflicts.” She commended the resilience of farmers and agricultural cooperatives and their essential role in strengthening food security, stressing the importance of accelerating project implementation and delivering tangible results as soon as possible. She also reaffirmed the World Bank’s continued support for Lebanon, including through periods of crisis, as it has done over the years.
+Thair Shraideh, UNDP Resident Representative a.i. in Lebanon, said: “This facility comes at a critical time for the recovery of Lebanon’s agricultural sector, helping farmers and cooperatives restore their productive capacity while investing in solutions that are more efficient, sustainable and better able to adapt to climate and economic challenges. Through our partnership with the Council for Development and Reconstruction, in collaboration with the Ministry of Agriculture and the Directorate General of Cooperatives, and with funding from the World Bank, we are working to turn grants into productive and sustainable investments that strengthen livelihoods and drive local economic recovery.”
+The facility falls under the Green Agri-food Transformation for Economic Recovery (GATE) project, a Government of Lebanon initiative funded by the World Bank that aims to strengthen the resilience of farmers and small and medium-sized enterprises operating in Lebanon’s agri-food sector.
+The overall GATE project is financed through a US$200 million loan from the World Bank. The component implemented by UNDP, in coordination with CDR, the Ministry of Agriculture and the Directorate General of Cooperatives, amounts to US$20 million and is dedicated to grants and technical assistance for eligible farmers, agricultural cooperatives and farmers’ associations.
+The initiative seeks to address key challenges facing Lebanon’s agricultural sector, including limited access to finance, rising production and energy costs, water scarcity, and increasing climate-related risks. By supporting climate-smart investments and strengthening farmers’ capacities, the facility will contribute to a more resilient, productive and competitive agricultural sector.
+Applications
+Eligible applicants can review the eligibility criteria and submit their applications through:
+Application link: https://www.undp.org/lebanon/grants
+Application deadline: 3 November 2026
+Background:
+GATE is financed through a World Bank loan to the Lebanese Republic and implemented by the Council for Development and Reconstruction (CDR) on behalf of the Government of Lebanon. The Ministry of Agriculture (MoA) and the General Directorate of Cooperatives (GDC) provide technical leadership and oversight for the Climate-Smart Matching Grants component, while UNDP provides implementation support.</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:54:14.615632+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Lebanese Red Cross, Ministry of Environment and UNDP Launch Initiative to Strengthen Community Participation in National Climate Policies</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/lebanon/press-releases/lebanese-red-cross-ministry-environment-and-undp-launch-initiative-strengthen-community-participation-national-climate</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Lebanese Red Cross, Ministry of Environment and UNDP Launch Initiative to Strengthen Community Participation in National Climate Policies
+October 12, 2026
+The Lebanese Red Cross, in collaboration with the Ministry of Environment and the United Nations Development Programme (UNDP), organized a national event today entitled “Towards Climate Policies That Are More Responsive to Local Communities” at the Lebanese Red Cross Training and Development Centre in Jounieh.
+The event was attended by Minister of Environment Dr. Tamara El Zein, UNDP Resident Representative a.i. Thair Shraideh, and representatives of governorates, unions of municipalities, municipalities and local communities.
+The event highlighted cooperation between the Ministry of Environment and the Lebanese Red Cross to support the integration of national climate policies into plans and programmes at both local and national levels, including the National Adaptation Plan (NAP) and the Nationally Determined Contributions (NDCs). It also aimed to strengthen the role of local communities and authorities and promote their active participation in climate-related decision-making.
+The event opened with welcoming remarks by Kassem Shaalan, Director of the Disaster Risk Reduction Unit at the Lebanese Red Cross, who highlighted the importance of the gathering and the Lebanese Red Cross’s work with communities across the country, particularly in communicating the NDCs and the National Adaptation Plan and understanding how communities engage with these frameworks.
+He also emphasized the role of the Lebanese Red Cross in maintaining a continuous link between national policies and local implementation, including following up with municipalities after training sessions to assess what has changed, what is working and where challenges remain.
+In his remarks, Shraideh stated: “We work with the Ministry of Environment, relevant institutions and municipalities to connect climate policies with action on the ground by strengthening coordination, building capacities and providing the information needed to make decisions that protect people and their livelihoods.”
+He added: “Our partnership with the Lebanese Red Cross is particularly important in this process, building on our joint work in disaster risk management and strengthening preparedness.”
+Minister of Environment Dr. Tamara El Zein addressed participants, stating: “Our responsibility today is not limited to developing strong national strategies. It also includes ensuring that these strategies are understood, that people feel they are relevant to their lives, and that they ultimately translate into concrete action across Lebanon.”
+The opening remarks were followed by a video presentation on the Nationally Determined Contributions and the National Adaptation Plan.
+The event also featured an interactive panel discussion moderated by Lea Kai, UNDP Climate Change Project Manager and Adviser to the Minister of Environment. The discussion explored local climate action priorities, the rationale behind the initiative, and the respective roles of the Ministry of Environment, the Lebanese Red Cross and UNDP. It also highlighted the importance of partnerships between national and local stakeholders in strengthening communities’ capacity to adapt to climate-related challenges.
+The session provided a platform for continued dialogue and collaboration, allowing representatives of participating institutions and communities to exchange perspectives and experiences and share their priorities and needs. These discussions will help identify future areas of work and priorities while strengthening climate action at the local level.</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:54:24.223228+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Ministry of Environment and UNDP Recognize 15 Technicians and Advance Digital Solutions for Energy-Efficient Cooling</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/lebanon/press-releases/ministry-environment-and-undp-recognize-15-technicians-and-advance-digital-solutions-energy-efficient-cooling</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Ministry of Environment and UNDP Recognize 15 Technicians and Advance Digital Solutions for Energy-Efficient Cooling
+October 2, 2026
+Beirut, 2 October 2026 – The Ministry of Environment and the United Nations Development Programme (UNDP) in Lebanon today recognized 15 top-performing technicians from among approximately 700 technicians and students who have benefited from training and capacity-building programmes in Lebanon’s refrigeration and air-conditioning sector.
+The 15 technicians completed specialized training in the digital monitoring of refrigeration systems and facilities, as part of efforts to improve energy efficiency, reduce emissions and promote more sustainable cooling practices.
+The training and capacity-building programmes combine technical expertise with digital tools and data to help sector professionals improve the performance of cooling systems, reduce energy consumption and emissions, and contribute to ozone layer protection and climate action.
+Minister of Environment Dr. Tamara Elzein said: “Improving the efficiency of refrigeration and air-conditioning systems is an important component of national priorities, given its environmental and economic implications and its direct impact on reducing electricity consumption, costs and emissions.” She noted that “the sector accounts for approximately 26% of Lebanon’s total reported electricity demand.”
+She added that “investment in modern technologies and national skills in this sector is no longer merely a technical matter, but part of addressing energy and environmental challenges and protecting the ozone layer, particularly as the need for cooling increases due to climate change.”
+UNDP Resident Representative in Lebanon a.i., Mr. Thair Shraideh, said: “The value of digital solutions lies not in the technology itself, but in the results they help achieve. Success is not measured by the number of sensors installed, but by the energy we save, the emissions we avoid, the costs we reduce, and our ability to scale effective solutions. Through our partnership with the Ministry of Environment and the National Ozone Unit, we are investing in national skills that can turn these tools into practical results.”
+This approach is being put into practice through a pilot application of digital monitoring solutions at Happy Supermarket in Beirut. The pilot aims to assess their effectiveness and measure their impact on energy consumption, emissions and costs, while generating evidence to inform the potential scale-up of effective solutions to other facilities.
+The Ministry of Environment and UNDP expressed their appreciation to the National Ozone Unit, trainers, vocational education and training institutions and schools, and all partners contributing to these efforts.
+The training and pilot application are part of a joint initiative by the Ministry of Environment and UNDP to promote more efficient digital solutions in Lebanon’s refrigeration and cold chain sector. The initiative contributes to reducing energy consumption and emissions and supports Lebanon’s commitments to ozone layer protection and climate action, including its Nationally Determined Contribution (NDC 3.0), the Montreal Protocol and the Kigali Amendment.</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:54:32.513604+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Bekaa and South Lebanon receive more than 20 machines and trucks to support waste services</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/lebanon/press-releases/bekaa-and-south-lebanon-receive-more-20-machines-and-trucks-support-waste-services</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>*Twenty-six pieces of equipment in total: 9 machines supporting three waste management facilities in the Bekaa and 17 collection trucks serving 15municipalities and unions of municipalities in South Lebanon
+Bekaa and South Lebanon receive more than 20 machines and trucks to support waste services
+September 8, 2026
+Saida, 8 September 2026 - The European Union (EU), the United Nations Development Programme (UNDP) and the Ministry of Environment have delivered essential waste management equipment to municipalities, unions of municipalities and waste management facilities across the Bekaa and South Lebanon.
+Funded by the European Union and implemented by UNDP in partnership with the Ministry of Environment, the support includes nine pieces of machinery for three facilities in the Bekaa and 17 waste collection trucks for 15 municipalities and unions of municipalities in South Lebanon. The equipment will strengthen day-to-day operations and help local authorities sustain waste collection and facility services amid continued financial and operational pressures.
+The deliveries were marked by separate handover events in the Bekaa and South Lebanon, bringing together the Ministry of Environment, the European Union, UNDP, local authorities and partners. The latest handover, held today at Saida Serail, took place in the presence of H.E. Dr. Tamara El Zein, Minister of Environment; H.E. Ms. Sandra De Waele, Ambassador of the European Union to Lebanon; and Mr. Thair Shraideh, UNDP Resident Representative a.i. in Lebanon, ; and Mr. Mansour Daou, Governor of South Lebanon, alongside representatives of municipalities and unions of municipalities.
+H.E. Dr. Tamara El Zein, Minister of Environment, said: “Strong waste management starts with strong municipalities. Equipping municipalities and waste management facilities in the Bekaa and South Lebanon with the tools they need means better services, stronger local capacity, and a healthier environment for communities.
+But equipment alone is not enough. We are putting in place the reforms needed to make the sector sustainable—from the adoption of the Cost Recovery Law and the update of the National Integrated Solid Waste Management Strategy to the activation of the National Solid Waste Management Authority.
+Together, we are moving from addressing immediate needs to building a waste management system that is sustainable, financially viable, efficient, and accountable—one that delivers better services for citizens and lasting solutions for Lebanon.”
+H.E. Ms. Sandra De Waele, Ambassador of the European Union to Lebanon, said: “Through the provision of essential waste management equipment to municipalities and facilities in the Bekaa and South Lebanon, the European Union is helping address urgent needs and maintain essential services for local communities. At the same time, we are helping the government find lasting solutions to the planning and financing of the sector, and we welcome the recent reforms undertaken in this regard. The European Union remains a reliable partner for Lebanon and its people, particularly in these challenging times.”
+Mr. Thair Shraideh, UNDP Resident Representative a.i. in Lebanon, said: “Local authorities are on the front line of waste management, often operating with very limited resources. This support responds to practical needs: trucks that help municipalities sustain collection services in the South and machinery that strengthens operations at three facilities in the Bekaa. Together with the Ministry of Environment and the European Union, UNDP is connecting these investments to the planning, governance and financing reforms needed for lasting improvement.”
+Mr. Mansour Daou, Governor of South Lebanon, thanked the European Union and UNDP for their support, saying: “We would have wished to come together under better circumstances, given the challenges South Lebanon is facing. We value every contribution that supports municipalities and helps our communities overcome this difficult period and move towards better conditions.”
+In the Bekaa, the equipment benefits waste management facilities serving Zahle, Baalbek and Joub Jannine. In South Lebanon, the beneficiaries are the municipalities of Arzoun, Ghazieh, Jbal El Botom, Maarake and Tyre, and the Unions of Municipalities of Bint Jbeil, Chekif, Hasbani, Jabal Amel, Ourqoub, Iqlim El Touffah, Jabal El Rihan, Qalaa, Jezzine and Sahel El Zahrani.
+Together, the two deliveries address immediate operational needs while advancing wider efforts to build a more sustainable and accountable solid waste management system. The equipment support is complemented by work on national planning, data and governance, municipal capacity development, and the financial sustainability of local waste services.</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:54:40.944767+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Norway Announces $1.5 Million in additional support to the Lebanese Armed Forces through UNDP</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/lebanon/press-releases/norway-announces-15-million-additional-support-lebanese-armed-forces-through-undp</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Norway Announces $1.5 Million in additional support to the Lebanese Armed Forces through UNDP
+August 26, 2026
+Saida, Lebanon, 26 August 2026 — Norwegian Minister of Foreign Affairs H.E. Mr. Espen Barth Eide announced an additional contribution of US$1.5 million in support of the Lebanese Armed Forces (LAF) through the United Nations Development Programme (UNDP), during a visit to the Mohammad Zgheib Barracks, headquarters of the LAF’s South Regional Command in Saida.
+During the visit, Minister Barth Eide was briefed on the LAF’s role and priorities, toured the barrack's healthcare facility - which serves as the main military medical hub for the south - visited a commissary rehabilitated with international support through UNDP, and was briefed on ongoing solarization works.
+In his remarks, the Lebanese Armed Forces Commander of South Sector, Brigadier General Andre Haddad said: “Your visit today represents an important milestone in our shared journey toward a stronger and more stable Lebanon. Norway's continued support reflects the depth of this partnership and the confidence placed in the vital role of the LAF in safeguarding Lebanon's sovereignty, unity and security.”
+Norwegian Minister of Foreign Affairs H.E. Mr. Espen Barth Eide said:
+"Norway has a long-standing engagement in support of Lebanon, and I am here to express my solidarity with the Lebanese people. In these challenging times, Norway reaffirms its support to the strengthening of Lebanon’s institutions and stability and remains committed to support the Lebanese Armed Forces in its endeavors to safeguard Lebanon´s security, sovereignty and territorial integrity.”
+UN Deputy Special Coordinator, Mr. Imran Riza said: “One thing Lebanese people can agree upon is the criticality of their army and, importantly, the need to ensure due support and dignity for its members. The LAF has a heavy burden on its shoulders as it stands at the vanguard of the extension of the authority of the Lebanese State. These efforts deserve the continued support of the international community. ”
+UNDP Resident Representative in Lebanon a.i. Mr. Thair Shraideh said: “Investing in the people who carry the institution is part of what enables the LAF to fulfil its mission. Supporting the everyday conditions of service eases the pressure on personnel and their families so they can carry out their duties. Norway’s consistent partnership allows us to respond to immediate pressures while investing in the LAF for the longer term, including through support to explosive ordnance clearance, which remains a precondition for the safe return of people to their homes and fields.”</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:54:50.408925+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>UNDP and the Lebanese Red Cross sign an MoU to strengthen cooperation on disaster management, climate resilience and risk-informed action in Lebanon</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/lebanon/press-releases/undp-and-lebanese-red-cross-sign-mou-strengthen-cooperation-disaster-management-climate-resilience-and-risk-informed-action</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>UNDP and the Lebanese Red Cross sign an MoU to strengthen cooperation on disaster management, climate resilience and risk-informed action in Lebanon | United Nations Development Programme
+UNDP works in about 170 countries and territories, helping to eradicate poverty, reduce inequalities and exclusion, and build resilience so countries can sustain progress. As the UN’s development agency, UNDP plays a critical role in helping countries achieve the Sustainable Development Goals.
+In order to achieve its mandate, UNDP relies entirely on voluntary contributions from UN Member States, multilateral organizations, private sector and other sources, in the form of unrestricted regular resources (core), and contributions earmarked for a specific theme, programme or project.
+Partnership is at the heart of everything UNDP does. We offer a nearly universal presence. Our substantial expertise—both intellectual acumen and practical experience—cuts across diverse development issues and settings.
+UNDP works in more than 170 countries and territories, helping to achieve the eradication of poverty and the reduction of inequalities and exclusion. We help countries develop policies, leadership skills, partnering abilities, institutional capabilities and build resilience in order to sustain development results.
+UNDP works with the Lebanese government, local institutions and communities to advance recovery, strengthen governance, create economic opportunities, address environmental challenges and promote sustainable development.
+Under the leadership of the Government of Lebanon, UNDP is supporting national and local institutions in advancing a coordinated, data-driven response. This includes strengthening institutional capacities, sustaining essential services, supporting frontline responders and municipalities, and promoting livelihoods, sustainable energy, and social cohesion.
+The Sustainable Development Goals (SDGs), otherwise known as the Global Goals, are a universal call to action to end poverty, protect the planet and ensure that all people enjoy peace and prosperity.
+Our News centre is a one-stop shop for multimedia press coverage and in-depth information on development-related issues. We provide news announcements, press releases and statements by UNDP leadership.
+UNDP publications showcase the organization’s thought leadership and expertise and play a key role in fulfilling our mandate to support the realisation of the SDGs and encourage global development.
+UNDP works in more than 170 countries and territories, helping to achieve the eradication of poverty and the reduction of inequalities and exclusion. We help countries develop policies, leadership skills, partnering abilities, institutional capabilities and build resilience in order to sustain development results.
+Explore UNDP Lebanon’s grant opportunities and calls for proposals supporting local organizations, communities and initiatives that advance sustainable development across the country.
+As a public organization entrusted with donor funds and committed to supporting developing economies, UNDP works to improve access to quality assured supplies in a cost effective and reliable way.
+UNDP and The Lebanese Red Cross Sign An MoU To Strengthen Cooperation On Disaster Management, Climate Resilience and Risk-informed Action In Lebanon
+UNDP and the Lebanese Red Cross sign an MoU to strengthen cooperation on disaster management, climate resilience and risk-informed action in Lebanon
+August 21, 2026
+►Listen
+Photo: UNDP Lebanon
+Today, UNDP's Resident Representative Blerta Aliko and the Lebanese Red Cross Secretary General Mr. Georges Kettaneh signed a Memorandum of Understanding to strengthen cooperation on disaster management and climate resilience in Lebanon.
+Building on years of collaboration, the MoU will support efforts to better prepare communities for emergencies, strengthen early action, and improve coordination in responding to future risks.
+The partnership brings together LRC’s strong presence across communities with UNDP’s work in support of Lebanon’s national disaster risk management and climate adaptation efforts.</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:54:58.891172+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Ministry of Public Works and Transport and UNDP Sign Partnership to Advance Public Sector Reform and Sustainable Infrastructure in Lebanon</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/lebanon/press-releases/ministry-public-works-and-transport-and-undp-sign-partnership-advance-public-sector-reform-and-sustainable-infrastructure</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Ministry of Public Works and Transport and UNDP Sign Partnership to Advance Public Sector Reform and Sustainable Infrastructure in Lebanon
+August 12, 2026
+Beirut, 12 August 2026 – The Ministry of Public Works and Transport (MoPWT), represented by its Minister, H.E. Mr. Fayez Rasamny, and the United Nations Development Programme (UNDP), represented by its Resident Representative in Lebanon, Ms. Blerta Aliko, signed a Memorandum of Understanding (MoU) establishing a strategic framework for cooperation to support institutional reform, improve public service delivery and advance sustainable infrastructure in Lebanon.
+The partnership will foster collaboration across a range of national priorities, including digital transformation, urban and territorial planning, sustainable public transport, maritime safety, port-sector development, and the sustainability and decarbonization of public assets. It also provides a framework for cooperation on crisis prevention, response and recovery, while supporting technical assistance and capacity development to enhance the Ministry’s planning and implementation capacities.
+H.E. Mr. Fayez Rasamny, Minister of Public Works and Transport, said: “UNDP has been a longstanding partner to Lebanon, supporting critical reforms and strengthening institutions across government. Today, we are already seeing the benefits of that partnership, and this Memorandum of Understanding marks an important step in deepening our cooperation.
+The Ministry of Public Works and Transport carries a vast mandate, spanning airports, ports, land borders, infrastructure and public transportation. At a time when the Ministry is operating with significant human-resource constraints, our priority is to empower our highly qualified teams with the capacity, expertise and international experience needed to deliver tangible reforms that citizens can see and feel.
+Lebanon cannot afford to lose time. We must advance the reforms and projects our country urgently needs while remaining ready to seize opportunities arising from a rapidly changing regional and geopolitical landscape. This MoU will provide essential support in capacity-building, institutional strengthening and reform implementation, helping us translate our plans and solutions into concrete results.
+We know what needs to be done, and we have a strong team committed to doing it. With the right support and partnerships, we can accelerate implementation, strengthen the Ministry’s ability to deliver, and build more efficient, resilient and modern transport and infrastructure systems for Lebanon.”
+Ms. Blerta Aliko, UNDP Resident Representative in Lebanon, said: Through this partnership, the Ministry of Public Works and Transport and UNDP reaffirm their shared commitment to advancing public sector reform, strengthening infrastructure governance, and delivering more efficient, resilient and sustainable public services for people across Lebanon.</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:55:07.354212+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UNDP_Lebanon.xlsx
+++ b/UNDP_Lebanon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8449,6 +8449,89 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>German Development Minister Visits Lebanese Civil Defense, Reaffirming Support for First Responders through UNDP</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/lebanon/press-releases/german-development-minister-visits-lebanese-civil-defense-reaffirming-support-first-responders-through-undp</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>German Development Minister Visits Lebanese Civil Defense, Reaffirming Support for First Responders through UNDP | United Nations Development Programme
+UNDP works in about 170 countries and territories, helping to eradicate poverty, reduce inequalities and exclusion, and build resilience so countries can sustain progress. As the UN’s development agency, UNDP plays a critical role in helping countries achieve the Sustainable Development Goals.
+In order to achieve its mandate, UNDP relies entirely on voluntary contributions from UN Member States, multilateral organizations, private sector and other sources, in the form of unrestricted regular resources (core), and contributions earmarked for a specific theme, programme or project.
+Partnership is at the heart of everything UNDP does. We offer a nearly universal presence. Our substantial expertise—both intellectual acumen and practical experience—cuts across diverse development issues and settings.
+UNDP works in more than 170 countries and territories, helping to achieve the eradication of poverty and the reduction of inequalities and exclusion. We help countries develop policies, leadership skills, partnering abilities, institutional capabilities and build resilience in order to sustain development results.
+UNDP works with the Lebanese government, local institutions and communities to advance recovery, strengthen governance, create economic opportunities, address environmental challenges and promote sustainable development.
+Under the leadership of the Government of Lebanon, UNDP is supporting national and local institutions in advancing a coordinated, data-driven response. This includes strengthening institutional capacities, sustaining essential services, supporting frontline responders and municipalities, and promoting livelihoods, sustainable energy, and social cohesion.
+The Sustainable Development Goals (SDGs), otherwise known as the Global Goals, are a universal call to action to end poverty, protect the planet and ensure that all people enjoy peace and prosperity.
+Our News centre is a one-stop shop for multimedia press coverage and in-depth information on development-related issues. We provide news announcements, press releases and statements by UNDP leadership.
+UNDP publications showcase the organization’s thought leadership and expertise and play a key role in fulfilling our mandate to support the realisation of the SDGs and encourage global development.
+UNDP works in more than 170 countries and territories, helping to achieve the eradication of poverty and the reduction of inequalities and exclusion. We help countries develop policies, leadership skills, partnering abilities, institutional capabilities and build resilience in order to sustain development results.
+Explore UNDP Lebanon’s grant opportunities and calls for proposals supporting local organizations, communities and initiatives that advance sustainable development across the country.
+As a public organization entrusted with donor funds and committed to supporting developing economies, UNDP works to improve access to quality assured supplies in a cost effective and reliable way.
+German Development Minister Visits Lebanese Civil Defense, Reaffirming Support For First Responders Through UNDP
+German Development Minister Visits Lebanese Civil Defense, Reaffirming Support for First Responders through UNDP
+October 30, 2026
+►Listen
+Beirut – 30 October 2026 — Today, Germany’s Federal Minister for Economic Cooperation and Development, H.E. Ms. Reem Alabali Radovan, visited the Lebanese Civil Defense Center in Tohwita, Beirut, together with UNDP Deputy Resident Representative a.i. Mr. Thair Al Shraideh. They were received by General Imad Khreich, Director General of the Lebanese Civil Defense, and 80 personnel of civil defense from different locations in Lebanon.
+The visit highlighted Germany’s continued support to the Lebanese Civil Defense, underscoring its viral role in protecting communities and responding to emergencies across Lebanon amid compounded crises, conflict-related pressures, climate risks, and limited public resources.
+With over 6.6 M. US-Dollars of funding from the Government of Germany through KfW Development Bank, the United Nations Development Programme has strengthened capacities of and procured equipment for Civil Defense across Lebanon. The support includes the construction and equipping of two Civil Defense centers in Minieh and Manara, as well as the provision of firefighting vehicles, ambulances, rescue equipment, protective gear, and operational tools.
+During the visit, the Minister and her delegation observed a live drill and toured an exhibition of German-funded equipment provided through UNDP, showcasing how sustained investment in emergency services is improving operational readiness, responder safety, and preparedness.
+The visit reaffirmed the continued partnership between the Government of Germany, UNDP, and the Lebanese Civil Defense to strengthen public institutions, support first responders, and improve assistance to people affected by armed conflict and crises across Lebanon.</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:34:53.052749+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ISF Inaugurates Rehabilitated Antelias Police Station with EU and UNDP Support to Strengthen Community Policing</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/lebanon/press-releases/isf-inaugurates-rehabilitated-antelias-police-station-eu-and-undp-support-strengthen-community-policing</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ISF Inaugurates Rehabilitated Antelias Police Station with EU and UNDP Support to Strengthen Community Policing
+October 30, 2026
+Antelias, 29 October 2026 - As part of the project to strengthen community policing in Lebanon, funded by the European Union with support from the United Nations Development Programme (UNDP), and within the plan to rehabilitate a number of model police stations, an inauguration ceremony was held on 29 October 2026 for the rehabilitated Antelias Police Station, part of the Territorial Gendarmerie Unit. The ceremony was attended by the European Union Ambassador to Lebanon, Ms. Sandra De Waele; UNDP Resident Representative a.i. in Lebanon, Mr. Thair Al Shraideh; and the Commander of the Territorial Gendarmerie Unit, Brigadier General Jean Awad, representing the Director General of the Internal Security Forces (ISF), Major General Raed Abdullah, alongside local dignitaries and relevant officers.
+The ceremony opened with the Lebanese national anthem, followed by remarks by Ms. De Waele, who reaffirmed the European Union’s continued support for the ISF. She noted that this support includes rehabilitating police facilities, providing vehicles and equipment, and strengthening the capacities of specialized units combating organized crime, cybercrime, terrorism and smuggling. She explained that the European Union Support Mission to Lebanon would contribute to developing ISF capacities through advisory support and specialized training, emphasizing the institution’s essential role in extending state authority throughout Lebanese territory, in accordance with UN Security Council Resolution 1701. She commended ISF officers and personnel for their efforts to maintain security and reaffirmed the European Union’s continued support for Lebanon and its security institutions. 
+For his part, Mr. Al Shraideh emphasized that the rehabilitation of Antelias Police Station marks an important milestone in the partnership between the ISF, the European Union and UNDP. He noted that the project aims to strengthen the institution’s operational capacities and improve services for citizens, particularly amid Lebanon’s security and economic challenges. He stressed the importance of cooperation with municipalities and local communities to strengthen preventive security, noting that European support also includes rehabilitating other police facilities and providing vehicles, equipment and training programmes to enhance ISF readiness and deployment across Lebanon.
+He highlighted the ISF’s pivotal role in extending state authority and protecting citizens, commending the efforts of its officers and personnel despite difficult conditions. He reaffirmed UNDP’s commitment to continuing its support for the institution and strengthening its capacity to fulfil its responsibilities.
+Brigadier General Awad also delivered remarks, affirming that the rehabilitation of Antelias Police Station represents an important step towards strengthening ISF capacities and improving its security services, helping to reinforce citizens’ trust in state institutions. He praised the dedication of ISF officers and personnel, who have continued to perform their duties despite security and economic challenges and difficult conditions. He stressed the importance of cooperation with municipalities and local communities to strengthen preventive security, highlighting initiatives that include improving lighting, conducting patrols on electric bicycles and carrying out awareness-raising activities. He also expressed appreciation for the European Union’s support and the partnership with UNDP in rehabilitating police facilities and providing equipment, vehicles and training to enhance the institution’s readiness and capacity to carry out its duties.
+He thanked all those who contributed to completing the project and reaffirmed the ISF’s commitment to maintaining security and stability and serving citizens.
+At the close of the ceremony, the delegation toured the station and viewed its departments and equipment. The event concluded with a group photograph.</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:35:01.849554+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UNDP_Lebanon.xlsx
+++ b/UNDP_Lebanon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E195"/>
+  <dimension ref="A1:E198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8532,6 +8532,116 @@
         </is>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Lebanon Recognizes 120 Ministry of Social Affairs Coordinators and Volunteers for Supporting Displaced Families During the Conflict</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/lebanon/press-releases/lebanon-recognizes-120-ministry-social-affairs-coordinators-and-volunteers-supporting-displaced-families-during-conflict</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Lebanon Recognizes 120 Ministry of Social Affairs Coordinators and Volunteers for Supporting Displaced Families During the Conflict
+August 11, 2026
+BEIRUT, 11 August 2026 –The Ministry of Social Affairs (MoSA), the European Union (EU) and the United Nations Development Programme (UNDP) recognized 120 Ministry of Social Affairs coordinators and volunteers who supported internally displaced persons (IDPs) in collective shelters throughout the recent conflict, following the completion of a programme to strengthen shelter coordination and preparedness for future emergencies.
+The ceremony was held at the Radisson Blu Hotel, Beirut Verdun, bringing together H.E. Ms. Haneen Sayed, Minister of Social Affairs; Mr. Samy Saadi, Chargé d’Affaires a.i of the European Union Delegation to Lebanon; and Mr. Thair Shraideh, UNDP Deputy Resident Representative in Lebanon, alongside representatives of the Lebanese Red Cross – Disaster Risk Management Unit in Beirut, the Lebanese University Task Force, shelter coordinators, volunteers and development partners.
+With the escalation of the conflict in March 2026 triggering a new wave of displacement, the Ministry of Social Affairs trained 120 coordinators and volunteers managing 154 collective shelters across Beirut, with funding from the European Union and support from UNDP and the Permanent Peace Movement. The programme supported the Ministry's response to the crisis, improving service delivery and coordination across shelters, while also strengthening its preparedness for future emergencies.
+H.E. Ms. Haneen Sayed, Minister of Social Affairs, said: “Throughout the recent response, Ministry of Social Affairs coordinators, social workers and volunteers played a critical role in supporting displaced families and ensuring that collective shelters remained responsive to people’s needs under extremely difficult conditions. Their dedication demonstrated the importance of investing in strong national and local capacities for emergency preparedness and response. We are deeply grateful to the European Union and UNDP for their partnership and support in strengthening these capacities, and to every coordinator and volunteer whose commitment, professionalism and service made this response possible.”
+Mr. Samy Saadi, Chargé d’Affaires a.i of the European Union Delegation to Lebanon, said: “Today's programme is one of several initiatives we have supported in recent months to help address this crisis, and crises like this one show us why institutions matter: it is strong institutions, not just emergency aid, that determine how well a country can respond. That is why, whether through this programme or through our direct partnership on the AMAN cash assistance programme and National Disability Allowance, our aim has been the same: to strengthen the Ministry's own ability to deliver, so that support reaches people reliably, through the Lebanese state itself.”
+"The Ministry of Social Affairs coordinators and volunteers have demonstrated true courage and commitment through their daily presence alongside displaced families under the most challenging conditions," said Mr. Thair Shraideh, UNDP Deputy Resident Representative in Lebanon. "This capacity-building program reflects UNDP's ongoing commitment to supporting Lebanese public institutions and local communities to strengthen emergency preparedness and uphold human dignity during times of crisis."
+The ceremony concluded with the presentation of certificates of completion to the 120 Ministry of Social Affairs coordinators and volunteers in recognition of their commitment and dedicated service to displaced families throughout the recent conflict.</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>2026-10-31T11:07:05.810194+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Lebanon Launches New National Planning Package to Strengthen Waste Management</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/lebanon/press-releases/lebanon-launches-new-national-planning-package-strengthen-waste-management</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Lebanon Launches New National Planning Package to Strengthen Waste Management
+July 22, 2026
+Beirut, Lebanon – 22 July 2026 – Today, Lebanon launched a comprehensive package of national studies and a Geographic Information System (GIS) platform* designed to strengthen waste management across the country. Funded by the European Union and implemented by the United Nations Development Programme (UNDP) in partnership with the Ministry of Environment, the package equips decision-makers with the data and tools needed to improve planning, prioritize investments, and advance more sustainable waste management solutions.
+The launch took place under the High Patronage of H.E. Dr. Tamara El Zein, Minister of Environment, and brought together H.E. Ms. Sandra De Waele, Ambassador of the European Union to Lebanon; Mr. Adel Gerges Al-Shabab, Director General of the Lebanese Ministry of Industry, representing H.E. Eng. Joe Issa El Khoury, Minister of Industry; Ms. Blerta Aliko, UNDP Resident Representative in Lebanon; as well as representatives from government institutions, municipalities, the private sector, academia, and development partners.
+Covering healthcare waste, e-waste, green waste, slaughterhouse waste, cardboard and paper waste, and waste-derived fuels, the package provides a comprehensive picture of Lebanon's waste management sector. Together, the studies and the national GIS platform equip national and local authorities with evidence and tools to identify service gaps, monitor infrastructure, coordinate interventions, and guide future policies and investments.
+“As Lebanon advances efforts to reform and modernize its waste management sector, access to reliable data, strategic planning tools, and sound technical evidence becomes increasingly important. The studies and GIS platform launched today will support improved governance, stronger institutional coordination, and more informed decision-making, helping national authorities including National Solid Waste Management Authority and Municipalities, prioritize investments and implement sustainable solutions that respond to both current needs and future challenges.” said H.E. Dr. Tamara Elzein, Minister of Environment.
+"Lebanon's waste sector represents an untapped investment opportunity. Every ton diverted from landfill into sorting, composting, or recycling becomes part of a value chain capable of generating revenue and attracting responsible capital that creates jobs, strengthens our export capacity, and reinforces the revival of Lebanon's industrial sector. Let us modify our model from “waste treatment to waste industrialization,” added Mr. Adel Gerges Al-Shabab, Director General of the Lebanese Ministry of Industry, representing H.E. Eng. Joe Issa El Khoury, Minister of Industry.
+"The European Union is proud to support Lebanon in developing the knowledge and tools needed to transform its waste management sector in light of the recent environmental reforms. Their real value, however, lies in how they are used. We encourage the Ministry of Env and the Solid Waste Authority to build on this evidence to guide policy decisions, prioritize investments, and implement the reforms needed to deliver sustainable waste management services for the benefit of all citizens," said H.E. Ms. Sandra De Waele, Ambassador of the European Union to Lebanon.
+"Investing in reliable data is one of the smartest investments we can make for sustainable development. These studies and the GIS platform provide the evidence needed to strengthen governance, guide investments, and accelerate Lebanon's transition towards a more sustainable and circular approach to waste management," said Ms. Blerta Aliko, UNDP Resident Representative in Lebanon.
+Years of successive crises have placed increasing pressure on Lebanon's solid waste sector, underscoring the need for better planning, stronger coordination, and more targeted investments. By providing a shared evidence base and modern planning tools, the initiative also strengthens collaboration among key stakeholders—including the Ministry of Environment, the Ministry of Public Health, the Ministry of Industry, municipalities, waste operators, and the newly established Solid Waste Management Authority—supporting a more integrated approach to waste management governance.
+Note to editors:
+The Geographic Information System (GIS) platform provides information on facility locations, operational status, treatment capacities, technologies, and service areas, offering government institutions, municipalities, development partners, and operators a centralized tool to support planning, investment prioritization, coordination, and emergency response.
+The National Studies are publicly available and can be accessed here</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>2026-10-31T11:07:15.438638+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>UNDP and Kuwait Fund Sign US$3 Million Partnership to Strengthen Public Services in Lebanon</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/lebanon/press-releases/undp-and-kuwait-fund-sign-us3-million-partnership-strengthen-public-services-lebanon</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>The partnership will help restore reliable electricity to essential public institutions through renewable energy, supporting Lebanon's recovery and sustainable development.
+UNDP and Kuwait Fund Sign US$3 Million Partnership to Strengthen Public Services in Lebanon
+July 21, 2026
+Kuwait City, 21 July 2026 – The United Nations Development Programme (UNDP) and the Kuwait Fund for Development (KFAED) today signed an agreement to implement the "Empowering Public Services with Solar Energy – Lebanon" initiative, a US$3 million partnership that will provide clean and renewable energy solutions across seven key public institutions to improve essential services and support Lebanon's sustainable recovery.
+Lebanon's prolonged economic and energy crisis has left many public institutions operating with only a few hours of electricity each day, disrupting the delivery of essential public services and increasing reliance on costly diesel generators. Through this partnership, seven priority public institutions will be equipped with solar photovoltaic systems and energy-efficiency upgrades, helping ensure more reliable electricity while reducing operating costs, greenhouse gas emissions, and dependence on fossil fuels. The initiative will also strengthen the capacity of engineers and facility managers to operate and maintain the systems, benefiting more than 500,000 people across the country.
+"Partnerships are essential to solving today's development challenges. For many years, UNDP and the Kuwait Fund have worked together to help countries advance sustainable development and build more resilient communities. Through this partnership we are strengthening public institutions, supporting climate action, and delivering lasting economic, social, and environmental benefits, Said Ms. Emma Morley, UNDP Resident Representative in Kuwait.
+Reaffirming the Kuwait Fund's commitment, Mr. Rashaid Ali Al-Bader, Acting Director General of KFAED, said: "Today's agreement with UNDP reflects the Kuwait Fund's longstanding partnership with international organizations and our continued commitment to supporting the people of Lebanon. Reliable energy is essential to ensuring the continuity of public services. Through this grant, we are supporting practical and sustainable solar energy solutions that will reduce operating costs, strengthen the reliability of essential public institutions, and reduce dependence on conventional energy sources. We are confident in UNDP's ability to deliver this project effectively and believe it will create lasting impact by strengthening institutional capacity and advancing the SDGs we jointly support."
+Beyond improving access to reliable electricity, the initiative will help public institutions reduce operating costs, lower greenhouse gas emissions, and deliver more reliable services to communities. By investing in sustainable public infrastructure, the partnership contributes to Lebanon's long-term environmental and development priorities while creating lasting benefits for people and the planet.
+"At a time when many public institutions continue to face severe energy challenges, the State of Kuwait and the Kuwait Fund are making a timely and strategic investment in Lebanon's public sector and its capacity to deliver essential services. This generous grant will strengthen the resilience of critical public institutions, ensure greater continuity of service delivery, and help reduce energy costs through sustainable solutions. Beyond its immediate impact, it reflects a shared commitment to supporting the Lebanese people, strengthening national institutions, and accelerating the country's transition toward a more resilient and sustainable energy future” said Ms Blerta Aliko, UNDP Resident Representative in Lebanon.
+The partnership reflects the shared commitment of UNDP and the Kuwait Fund to supporting Lebanon's recovery through long-term investments in clean energy, stronger public institutions, and sustainable development. By improving the reliability and sustainability of essential public services, the initiative will help build more resilient institutions while contributing to a greener and more sustainable future for Lebanon.</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2026-10-31T11:07:25.094421+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
